--- a/ui_runner/templates/graded_analysis_tabs_2026-05-06.xlsx
+++ b/ui_runner/templates/graded_analysis_tabs_2026-05-06.xlsx
@@ -471,13 +471,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>26</v>
+      </c>
+      <c r="G2" t="n">
+        <v>64.90000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -497,12 +500,15 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -523,13 +529,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>23</v>
+      </c>
+      <c r="G4" t="n">
+        <v>48.9</v>
       </c>
     </row>
     <row r="5">
@@ -575,13 +584,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>40</v>
+      </c>
+      <c r="G6" t="n">
+        <v>27.3</v>
       </c>
     </row>
     <row r="7">
@@ -627,13 +639,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>418</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>260</v>
+      </c>
+      <c r="G8" t="n">
+        <v>37.8</v>
       </c>
     </row>
     <row r="9">
@@ -653,13 +668,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="G9" t="n">
+        <v>52.2</v>
       </c>
     </row>
     <row r="10">
@@ -679,13 +697,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>806</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>506</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>300</v>
+      </c>
+      <c r="G10" t="n">
+        <v>62.8</v>
       </c>
     </row>
     <row r="11">
@@ -705,13 +726,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>227</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>76</v>
+      </c>
+      <c r="G11" t="n">
+        <v>66.5</v>
       </c>
     </row>
     <row r="12">
@@ -731,13 +755,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>55</v>
+      </c>
+      <c r="G12" t="n">
+        <v>71.8</v>
       </c>
     </row>
     <row r="13">
@@ -757,13 +784,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>73</v>
+      </c>
+      <c r="G13" t="n">
+        <v>51.7</v>
       </c>
     </row>
     <row r="14">
@@ -783,13 +813,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>130</v>
+      </c>
+      <c r="G14" t="n">
+        <v>18.2</v>
       </c>
     </row>
     <row r="15">
@@ -809,13 +842,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>106</v>
+      </c>
+      <c r="G15" t="n">
+        <v>15.2</v>
       </c>
     </row>
     <row r="16">
@@ -835,13 +871,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>32</v>
+      </c>
+      <c r="G16" t="n">
+        <v>41.8</v>
       </c>
     </row>
     <row r="17">
@@ -861,13 +900,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>2467</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>507</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1960</v>
+      </c>
+      <c r="G17" t="n">
+        <v>20.6</v>
       </c>
     </row>
   </sheetData>
@@ -1057,32 +1099,56 @@
           <t>Elite</t>
         </is>
       </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>49</v>
+      </c>
+      <c r="D2" t="n">
+        <v>95</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>20</v>
+      </c>
+      <c r="F2" t="n">
+        <v>91.7</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>24</v>
+      </c>
+      <c r="H2" t="n">
+        <v>80.8</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>26</v>
+      </c>
+      <c r="J2" t="n">
+        <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
+      <c r="N2" t="n">
+        <v>83.3</v>
+      </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="P2" t="n">
+        <v>25</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>20</v>
+      </c>
+      <c r="R2" t="n">
+        <v>83.3</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1090,11 +1156,17 @@
       <c r="W2" t="n">
         <v>0</v>
       </c>
+      <c r="X2" t="n">
+        <v>41.5</v>
+      </c>
       <c r="Y2" t="n">
+        <v>53</v>
+      </c>
+      <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -1102,8 +1174,11 @@
       <c r="AE2" t="n">
         <v>0</v>
       </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -1112,41 +1187,74 @@
           <t>Above Avg</t>
         </is>
       </c>
+      <c r="B3" t="n">
+        <v>66.09999999999999</v>
+      </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>109</v>
+      </c>
+      <c r="D3" t="n">
+        <v>65.5</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>84</v>
+      </c>
+      <c r="F3" t="n">
+        <v>64.5</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>62</v>
+      </c>
+      <c r="H3" t="n">
+        <v>41.3</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>92</v>
+      </c>
+      <c r="J3" t="n">
+        <v>33.3</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="L3" t="n">
+        <v>18.2</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="N3" t="n">
+        <v>40</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="P3" t="n">
+        <v>23</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>113</v>
+      </c>
+      <c r="R3" t="n">
+        <v>65.40000000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>26</v>
+      </c>
+      <c r="T3" t="n">
+        <v>100</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
+      <c r="X3" t="n">
+        <v>30.1</v>
+      </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -1157,8 +1265,11 @@
       <c r="AE3" t="n">
         <v>0</v>
       </c>
+      <c r="AF3" t="n">
+        <v>53.8</v>
+      </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -1222,32 +1333,59 @@
           <t>Below Avg</t>
         </is>
       </c>
+      <c r="B5" t="n">
+        <v>85.09999999999999</v>
+      </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>47</v>
+      </c>
+      <c r="D5" t="n">
+        <v>78.59999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>42</v>
+      </c>
+      <c r="F5" t="n">
+        <v>77.09999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>35</v>
+      </c>
+      <c r="H5" t="n">
+        <v>58.8</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>17</v>
+      </c>
+      <c r="J5" t="n">
+        <v>33.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="L5" t="n">
+        <v>50</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="N5" t="n">
+        <v>77.8</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="P5" t="n">
+        <v>13.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>29</v>
+      </c>
+      <c r="R5" t="n">
+        <v>64.3</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1255,8 +1393,11 @@
       <c r="W5" t="n">
         <v>0</v>
       </c>
+      <c r="X5" t="n">
+        <v>51</v>
+      </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1267,8 +1408,11 @@
       <c r="AE5" t="n">
         <v>0</v>
       </c>
+      <c r="AF5" t="n">
+        <v>62.5</v>
+      </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -1332,44 +1476,83 @@
           <t>Total</t>
         </is>
       </c>
+      <c r="B7" t="n">
+        <v>62.8</v>
+      </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>806</v>
+      </c>
+      <c r="D7" t="n">
+        <v>66.5</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>227</v>
+      </c>
+      <c r="F7" t="n">
+        <v>71.8</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>195</v>
+      </c>
+      <c r="H7" t="n">
+        <v>51.7</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>151</v>
+      </c>
+      <c r="J7" t="n">
+        <v>18.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>159</v>
+      </c>
+      <c r="L7" t="n">
+        <v>15.2</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>125</v>
+      </c>
+      <c r="N7" t="n">
+        <v>41.8</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>55</v>
+      </c>
+      <c r="P7" t="n">
+        <v>20.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2467</v>
+      </c>
+      <c r="R7" t="n">
+        <v>64.90000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>74</v>
+      </c>
+      <c r="T7" t="n">
+        <v>48.9</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>45</v>
+      </c>
+      <c r="V7" t="n">
+        <v>27.3</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>55</v>
+      </c>
+      <c r="X7" t="n">
+        <v>37.8</v>
       </c>
       <c r="Y7" t="n">
+        <v>418</v>
+      </c>
+      <c r="Z7" t="n">
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1377,8 +1560,11 @@
       <c r="AE7" t="n">
         <v>0</v>
       </c>
+      <c r="AF7" t="n">
+        <v>52.2</v>
+      </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/ui_runner/templates/graded_analysis_tabs_2026-05-06.xlsx
+++ b/ui_runner/templates/graded_analysis_tabs_2026-05-06.xlsx
@@ -471,16 +471,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="E2" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="F2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G2" t="n">
-        <v>64.90000000000001</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -529,16 +529,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="E4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" t="n">
         <v>22</v>
       </c>
-      <c r="F4" t="n">
-        <v>23</v>
-      </c>
       <c r="G4" t="n">
-        <v>48.9</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="5">
@@ -558,13 +558,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -584,16 +587,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="E6" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G6" t="n">
         <v>40</v>
-      </c>
-      <c r="G6" t="n">
-        <v>27.3</v>
       </c>
     </row>
     <row r="7">
@@ -613,13 +616,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="8">
@@ -639,16 +645,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>418</v>
+        <v>504</v>
       </c>
       <c r="E8" t="n">
-        <v>158</v>
+        <v>210</v>
       </c>
       <c r="F8" t="n">
-        <v>260</v>
+        <v>294</v>
       </c>
       <c r="G8" t="n">
-        <v>37.8</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="9">
@@ -668,16 +674,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G9" t="n">
-        <v>52.2</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="10">
@@ -697,16 +703,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>806</v>
+        <v>822</v>
       </c>
       <c r="E10" t="n">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="F10" t="n">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="G10" t="n">
-        <v>62.8</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="11">
@@ -726,16 +732,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E11" t="n">
         <v>151</v>
       </c>
       <c r="F11" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G11" t="n">
-        <v>66.5</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="12">
@@ -755,16 +761,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E12" t="n">
         <v>140</v>
       </c>
       <c r="F12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G12" t="n">
-        <v>71.8</v>
+        <v>71.09999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -813,16 +819,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>159</v>
+        <v>120</v>
       </c>
       <c r="E14" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F14" t="n">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="G14" t="n">
-        <v>18.2</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="15">
@@ -842,16 +848,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>125</v>
+        <v>162</v>
       </c>
       <c r="E15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F15" t="n">
-        <v>106</v>
+        <v>142</v>
       </c>
       <c r="G15" t="n">
-        <v>15.2</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="16">
@@ -871,16 +877,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="E16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F16" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G16" t="n">
-        <v>41.8</v>
+        <v>39.3</v>
       </c>
     </row>
     <row r="17">
@@ -900,16 +906,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2467</v>
+        <v>2551</v>
       </c>
       <c r="E17" t="n">
-        <v>507</v>
+        <v>531</v>
       </c>
       <c r="F17" t="n">
-        <v>1960</v>
+        <v>2020</v>
       </c>
       <c r="G17" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
     </row>
   </sheetData>
@@ -1127,10 +1133,13 @@
         <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>100</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
         <v>83.3</v>
@@ -1144,11 +1153,8 @@
       <c r="Q2" t="n">
         <v>20</v>
       </c>
-      <c r="R2" t="n">
-        <v>83.3</v>
-      </c>
       <c r="S2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1157,28 +1163,28 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>41.5</v>
+        <v>49.2</v>
       </c>
       <c r="Y2" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
         <v>1</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -1212,64 +1218,64 @@
         <v>92</v>
       </c>
       <c r="J3" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="K3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L3" t="n">
-        <v>18.2</v>
+        <v>14.3</v>
       </c>
       <c r="M3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="N3" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="O3" t="n">
+        <v>19</v>
+      </c>
+      <c r="P3" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>116</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>243</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>50</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF3" t="n">
         <v>40</v>
       </c>
-      <c r="O3" t="n">
-        <v>15</v>
-      </c>
-      <c r="P3" t="n">
-        <v>23</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>113</v>
-      </c>
-      <c r="R3" t="n">
-        <v>65.40000000000001</v>
-      </c>
-      <c r="S3" t="n">
-        <v>26</v>
-      </c>
-      <c r="T3" t="n">
-        <v>100</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>216</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>53.8</v>
-      </c>
       <c r="AG3" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -1358,34 +1364,31 @@
         <v>17</v>
       </c>
       <c r="J5" t="n">
-        <v>33.3</v>
+        <v>37.5</v>
       </c>
       <c r="K5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L5" t="n">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="M5" t="n">
         <v>8</v>
       </c>
       <c r="N5" t="n">
-        <v>77.8</v>
+        <v>63.6</v>
       </c>
       <c r="O5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P5" t="n">
-        <v>13.8</v>
+        <v>19.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>29</v>
-      </c>
-      <c r="R5" t="n">
-        <v>64.3</v>
+        <v>31</v>
       </c>
       <c r="S5" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1394,25 +1397,31 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>51</v>
+        <v>52.7</v>
       </c>
       <c r="Y5" t="n">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
+      <c r="AB5" t="n">
+        <v>100</v>
+      </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>100</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF5" t="n">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -1477,22 +1486,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>62.8</v>
+        <v>63.3</v>
       </c>
       <c r="C7" t="n">
-        <v>806</v>
+        <v>822</v>
       </c>
       <c r="D7" t="n">
-        <v>66.5</v>
+        <v>66.2</v>
       </c>
       <c r="E7" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F7" t="n">
-        <v>71.8</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H7" t="n">
         <v>51.7</v>
@@ -1501,70 +1510,76 @@
         <v>151</v>
       </c>
       <c r="J7" t="n">
-        <v>18.2</v>
+        <v>20.8</v>
       </c>
       <c r="K7" t="n">
-        <v>159</v>
+        <v>120</v>
       </c>
       <c r="L7" t="n">
-        <v>15.2</v>
+        <v>12.3</v>
       </c>
       <c r="M7" t="n">
-        <v>125</v>
+        <v>162</v>
       </c>
       <c r="N7" t="n">
-        <v>41.8</v>
+        <v>39.3</v>
       </c>
       <c r="O7" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="P7" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>2467</v>
+        <v>2551</v>
       </c>
       <c r="R7" t="n">
-        <v>64.90000000000001</v>
+        <v>50</v>
       </c>
       <c r="S7" t="n">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="T7" t="n">
-        <v>48.9</v>
+        <v>24.1</v>
       </c>
       <c r="U7" t="n">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="V7" t="n">
-        <v>27.3</v>
+        <v>40</v>
       </c>
       <c r="W7" t="n">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="X7" t="n">
-        <v>37.8</v>
+        <v>41.7</v>
       </c>
       <c r="Y7" t="n">
-        <v>418</v>
+        <v>504</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>100</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>70</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AF7" t="n">
-        <v>52.2</v>
+        <v>22.2</v>
       </c>
       <c r="AG7" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/ui_runner/templates/graded_analysis_tabs_2026-05-06.xlsx
+++ b/ui_runner/templates/graded_analysis_tabs_2026-05-06.xlsx
@@ -906,13 +906,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2551</v>
+        <v>2561</v>
       </c>
       <c r="E17" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F17" t="n">
-        <v>2020</v>
+        <v>2029</v>
       </c>
       <c r="G17" t="n">
         <v>20.8</v>
@@ -1451,8 +1451,11 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
+      <c r="P6" t="n">
+        <v>10</v>
+      </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1531,7 +1534,7 @@
         <v>20.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>2551</v>
+        <v>2561</v>
       </c>
       <c r="R7" t="n">
         <v>50</v>
